--- a/artfynd/A 56676-2022 artfynd.xlsx
+++ b/artfynd/A 56676-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56676-2022 artfynd.xlsx
+++ b/artfynd/A 56676-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,376 +1394,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>113460451</v>
-      </c>
-      <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Hartjärnet, V om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>370075</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6619469</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>S-Arv-0826</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>113460452</v>
-      </c>
-      <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Hartjärnet, V om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>370122</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6619406</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>S-Arv-0825</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vid koordinat 64 ex. Även vid RT90: 6623274 - 1324781, noggrannhet 25 m, 46 ex.</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>113460450</v>
-      </c>
-      <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Hartjärnet, V om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>370038</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6619529</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>S-Arv-0827</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vid koordinat 42 ex. Även vid RT90: 6623377 - 1324664, noggrannhet 25 m, 28 ex.</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56676-2022 artfynd.xlsx
+++ b/artfynd/A 56676-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>3059240</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370116.0747119326</v>
+        <v>370116</v>
       </c>
       <c r="R2" t="n">
-        <v>6619416.653219221</v>
+        <v>6619417</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2012-01-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-01-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109108739</v>
+        <v>109108495</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -856,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370034.0489460127</v>
+        <v>370038</v>
       </c>
       <c r="R3" t="n">
-        <v>6619502.872506012</v>
+        <v>6619529</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,19 +869,9 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109108495</v>
+        <v>109108739</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>370037.9777680152</v>
+        <v>370035</v>
       </c>
       <c r="R4" t="n">
-        <v>6619528.502677444</v>
+        <v>6619503</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,19 +971,9 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109109461</v>
+        <v>109108955</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1030,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1090,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>370152.4849397282</v>
+        <v>370076</v>
       </c>
       <c r="R5" t="n">
-        <v>6619401.23981926</v>
+        <v>6619470</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,19 +1073,9 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,15 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109108955</v>
+        <v>109109321</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1132,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1207,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>370075.3862352034</v>
+        <v>370123</v>
       </c>
       <c r="R6" t="n">
-        <v>6619469.098507496</v>
+        <v>6619405</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,19 +1175,9 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109109321</v>
+        <v>109109461</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1234,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1324,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370122.2775896558</v>
+        <v>370152</v>
       </c>
       <c r="R7" t="n">
-        <v>6619405.827244952</v>
+        <v>6619401</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,19 +1277,9 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,6 +1303,241 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113460451</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hartjärnet, V om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>370075</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619469</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>S-Arv-0826</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113460452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hartjärnet, V om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>370122</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>S-Arv-0825</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid koordinat 64 ex. Även vid RT90: 6623274 - 1324781, noggrannhet 25 m, 46 ex.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
